--- a/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de horas que duerme</t>
+          <t>Menores según del número de horas que duerme (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 9,95</t>
+          <t>9,5; 9,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 10,0</t>
+          <t>9,54; 10,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,16</t>
+          <t>9,69; 10,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,24</t>
+          <t>8,94; 9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,92</t>
+          <t>9,45; 9,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 10,08</t>
+          <t>9,53; 10,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,9</t>
+          <t>9,45; 9,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 9,3</t>
+          <t>8,87; 9,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,86</t>
+          <t>9,53; 9,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 9,95</t>
+          <t>9,61; 9,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 9,94</t>
+          <t>9,62; 9,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 9,21</t>
+          <t>8,94; 9,22</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,94</t>
+          <t>9,55; 9,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 10,01</t>
+          <t>9,6; 9,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,29</t>
+          <t>9,03; 9,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,37 +881,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 10,15</t>
+          <t>9,75; 10,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,64</t>
+          <t>9,33; 9,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,36</t>
+          <t>9,09; 9,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 9,87</t>
+          <t>9,6; 9,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,02</t>
+          <t>9,72; 10,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,6</t>
+          <t>9,37; 9,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,29</t>
+          <t>9,1; 9,28</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,32; 9,75</t>
+          <t>9,34; 9,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,63; 10,13</t>
+          <t>9,64; 10,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,79</t>
+          <t>9,39; 9,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,35</t>
+          <t>9,06; 9,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,82</t>
+          <t>9,39; 9,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 10,12</t>
+          <t>9,69; 10,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 9,48</t>
+          <t>9,14; 9,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 9,06</t>
+          <t>8,73; 9,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,7</t>
+          <t>9,42; 9,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 10,04</t>
+          <t>9,72; 10,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,56</t>
+          <t>9,31; 9,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,16</t>
+          <t>8,94; 9,15</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,69</t>
+          <t>9,37; 9,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 9,99</t>
+          <t>9,58; 10,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,71</t>
+          <t>9,37; 9,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 9,23</t>
+          <t>8,94; 9,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,75</t>
+          <t>9,42; 9,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,85</t>
+          <t>9,41; 9,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,83</t>
+          <t>9,44; 9,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,23</t>
+          <t>8,95; 9,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,85</t>
+          <t>9,57; 9,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,7</t>
+          <t>9,45; 9,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,17</t>
+          <t>8,97; 9,19</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,71</t>
+          <t>9,53; 9,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,91</t>
+          <t>9,68; 9,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 9,21</t>
+          <t>9,06; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 9,73</t>
+          <t>9,55; 9,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,93</t>
+          <t>9,71; 9,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,6</t>
+          <t>9,41; 9,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,16</t>
+          <t>8,99; 9,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,7</t>
+          <t>9,56; 9,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,88</t>
+          <t>9,73; 9,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,62</t>
+          <t>9,49; 9,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,15</t>
+          <t>9,05; 9,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
@@ -716,47 +716,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 9,93</t>
+          <t>9,52; 9,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 10,0</t>
+          <t>9,54; 10,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,19</t>
+          <t>9,68; 10,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,24</t>
+          <t>8,94; 9,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,93</t>
+          <t>9,44; 9,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 10,09</t>
+          <t>9,54; 10,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,85</t>
+          <t>9,44; 9,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 9,29</t>
+          <t>8,86; 9,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,87</t>
+          <t>9,53; 9,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 9,95</t>
+          <t>9,63; 9,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,22</t>
+          <t>8,95; 9,23</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,95</t>
+          <t>9,55; 9,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 9,99</t>
+          <t>9,6; 9,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 9,68</t>
+          <t>9,32; 9,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +876,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,91</t>
+          <t>9,56; 9,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 10,17</t>
+          <t>9,74; 10,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,65</t>
+          <t>9,34; 9,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 9,36</t>
+          <t>9,1; 9,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 9,86</t>
+          <t>9,62; 9,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 10,02</t>
+          <t>9,72; 10,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,61</t>
+          <t>9,37; 9,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,28</t>
+          <t>9,11; 9,29</t>
         </is>
       </c>
     </row>
@@ -1001,32 +1001,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,14</t>
+          <t>9,63; 10,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,8</t>
+          <t>9,38; 9,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,36</t>
+          <t>9,05; 9,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,81</t>
+          <t>9,36; 9,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,12</t>
+          <t>9,71; 10,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 9,49</t>
+          <t>9,15; 9,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,22 +1036,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,7</t>
+          <t>9,41; 9,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 10,05</t>
+          <t>9,73; 10,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,56</t>
+          <t>9,31; 9,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,15</t>
+          <t>8,95; 9,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,68</t>
+          <t>9,38; 9,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,0</t>
+          <t>9,59; 10,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,71</t>
+          <t>9,38; 9,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,22</t>
+          <t>8,92; 9,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,74</t>
+          <t>9,41; 9,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,82</t>
+          <t>9,43; 9,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,83</t>
+          <t>9,42; 9,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,23</t>
+          <t>8,93; 9,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,67</t>
+          <t>9,44; 9,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,86</t>
+          <t>9,57; 9,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,71</t>
+          <t>9,45; 9,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 9,19</t>
+          <t>8,96; 9,18</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 9,9</t>
+          <t>9,7; 9,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,37 +1291,37 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,21</t>
+          <t>9,07; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,74</t>
+          <t>9,55; 9,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 9,92</t>
+          <t>9,71; 9,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,61</t>
+          <t>9,42; 9,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,15</t>
+          <t>9,0; 9,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,7</t>
+          <t>9,57; 9,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,88</t>
+          <t>9,73; 9,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,16</t>
+          <t>9,05; 9,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,77</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,08</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,76</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,66</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,65</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,97</t>
+          <t>9,46; 9,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 10,01</t>
+          <t>9,54; 10,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 10,17</t>
+          <t>9,44; 9,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,25</t>
+          <t>8,91; 9,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,92</t>
+          <t>9,5; 9,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 10,1</t>
+          <t>9,53; 10,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,88</t>
+          <t>9,69; 10,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 9,32</t>
+          <t>8,92; 9,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 9,97</t>
+          <t>9,6; 9,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 9,94</t>
+          <t>9,61; 9,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,23</t>
+          <t>8,95; 9,2</t>
         </is>
       </c>
     </row>
@@ -793,44 +793,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>9,94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,48</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,18</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,73</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>9,77</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,49</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,16</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9,1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9,73</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,94</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,48</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,73</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9,86</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>9,14</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,96</t>
+          <t>9,56; 9,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 9,98</t>
+          <t>9,74; 10,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 9,66</t>
+          <t>9,34; 9,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,31</t>
+          <t>9,07; 9,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,9</t>
+          <t>9,55; 9,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 10,18</t>
+          <t>9,6; 10,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,65</t>
+          <t>9,35; 9,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,35</t>
+          <t>8,99; 9,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 9,88</t>
+          <t>9,61; 9,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 10,01</t>
+          <t>9,73; 10,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,62</t>
+          <t>9,37; 9,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,29</t>
+          <t>9,06; 9,23</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,9</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,3</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,85</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,87</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,58</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,58</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,9</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,3</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>9,21</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>9,02</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,74</t>
+          <t>9,38; 9,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,63; 10,16</t>
+          <t>9,68; 10,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,8</t>
+          <t>9,15; 9,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,35</t>
+          <t>8,68; 9,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,79</t>
+          <t>9,32; 9,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 10,14</t>
+          <t>9,63; 10,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 9,49</t>
+          <t>9,39; 9,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,73; 9,05</t>
+          <t>9,07; 9,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,71</t>
+          <t>9,41; 9,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,08</t>
+          <t>9,71; 10,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,57</t>
+          <t>9,3; 9,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,16</t>
+          <t>8,91; 9,14</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,61</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,08</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,78</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,54</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,07</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,57</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1136,52 +1136,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,7</t>
+          <t>9,43; 9,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 10,01</t>
+          <t>9,45; 9,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,72</t>
+          <t>9,43; 9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>8,94; 9,25</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,37; 9,69</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,58; 9,99</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9,38; 9,71</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8,92; 9,21</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,41; 9,74</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 9,82</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,81</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8,93; 9,23</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,66</t>
+          <t>9,44; 9,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,85</t>
+          <t>9,56; 9,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,18</t>
+          <t>8,96; 9,16</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,81</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,51</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,79</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,6</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9,8</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9,55</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>9,08</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,72</t>
+          <t>9,54; 9,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 9,91</t>
+          <t>9,72; 9,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>9,42; 9,6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8,99; 9,14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,52; 9,71</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,69; 9,91</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>9,51; 9,7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 9,21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,55; 9,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 9,94</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,6</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,16</t>
+          <t>9,04; 9,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,89</t>
+          <t>9,72; 9,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,62</t>
+          <t>9,48; 9,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,15</t>
+          <t>9,03; 9,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,65</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,76</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9,76</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,07</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>9.662274371957151</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>9.768805512672261</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.650662007048981</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>9.076724752810426</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>9.706322516243066</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>9.755176063402335</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>9.901795726663732</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>9.059398507852558</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>9.683154285547216</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>9.762331301363551</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>9.769825825863943</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.068237534255486</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>9,46; 9,92</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,54; 10,08</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9,44; 9,9</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8,91; 9,32</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,5; 9,95</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,53; 10,0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 10,16</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,92; 9,21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9,53; 9,86</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9,6; 9,95</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9,61; 9,94</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,95; 9,2</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>9.46048333191537</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>9.535484764276662</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>9.439422208132218</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>8.91307751050034</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>9.500046705106179</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>9.530309832607685</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>9.690564787650024</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>8.923085192919556</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>9.52938454908805</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>9.600992140309565</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>9.608570779689117</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>8.951509832684795</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.915892253938395</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.07964955857859</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.898165958417749</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.316675052720944</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.952246882074778</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>9.996199451098029</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>10.1610812163063</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>9.205154221892371</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>9.856981636610758</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>9.951531396586871</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>9.935196648191079</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>9.204941607629536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,73</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,48</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,18</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,73</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,49</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,73</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9,49</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,56; 9,91</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9,74; 10,15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,34; 9,64</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 9,31</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,55; 9,94</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,6; 10,01</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,35; 9,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8,99; 9,21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9,61; 9,87</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9,73; 10,02</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9,37; 9,6</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 9,23</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>9.726904159065819</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>9.940870160720069</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9.478845451937005</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9.17908914654568</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>9.73069208479073</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>9.774958137462166</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9.491794758582076</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>9.096547252181638</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>9.728719060290359</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>9.861160517763576</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>9.485055232636968</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.142985998420411</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9,58</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,9</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,85</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,52</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,87</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,58</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9,89</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>9,02</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9.560884297572077</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>9.738830890085772</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>9.337372274183441</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9.065147765816508</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>9.545014653952421</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>9.604272789169606</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>9.345619369574846</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>8.987484748763517</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>9.607966778862208</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>9.730243585527525</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>9.368088668638901</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>9.06238683177312</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>9,38; 9,82</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,68; 10,12</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,15; 9,48</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8,68; 9,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,32; 9,75</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,63; 10,13</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,39; 9,79</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 9,37</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9,41; 9,7</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 10,04</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9,3; 9,56</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,91; 9,14</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.910191888166878</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.14756096857579</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.644937782626418</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.313427422336835</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>9.940347729999731</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>10.00846289305731</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>9.678108987090649</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>9.208693792990536</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>9.873189773993243</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>10.0185600966897</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9.603376324425506</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>9.233341016683218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,57</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,78</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9,7</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9,57</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,07</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>9.579104970183755</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.899630745213617</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.302398780320424</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>8.847046292021016</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9.524752537140678</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>9.871222770300909</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>9.576261407265251</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>9.210921576141379</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9.553094017088918</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>9.885952458922885</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>9.434596595709387</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>9.02130726965407</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 9,75</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9,45; 9,85</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 9,83</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8,94; 9,25</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,37; 9,69</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,58; 9,99</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,38; 9,71</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8,92; 9,21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9,44; 9,67</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9,56; 9,85</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9,45; 9,7</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,96; 9,16</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>9.381340229398731</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9.681551167714225</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9.148405012382455</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>8.675077293378699</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>9.31770513971618</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>9.633545167365734</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>9.394446390893989</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>9.066172815251353</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>9.413202990943445</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>9.712661686193483</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>9.304233069853282</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>8.908541923699767</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.824579551068313</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.11516371041762</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.48148140623047</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.00434237067403</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>9.747008010066772</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10.1336050052726</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>9.790092204610552</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.37065324594499</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9.70112135887892</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>10.04245321889133</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>9.56439472546962</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>9.140903089591271</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>9.57104163052658</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>9.621072794840826</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9.606915109441561</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.083933470675253</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>9.52747036501329</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>9.776149977118754</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>9.53515743924399</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>9.055602111098555</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9.549263333766877</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>9.698818698417771</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>9.570688877315673</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>9.069944997413323</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>9.427337017615141</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>9.450853499427332</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>9.433439003601496</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8.942007067610135</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>9.371214655082781</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>9.575910944494582</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>9.380531714031608</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>8.916885347184818</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>9.438013684295164</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>9.560186884249422</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>9.451630952306914</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>8.962367080475165</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.754196953749696</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.853278283660044</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.830577744149592</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>9.251315337092128</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>9.686209145722593</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>9.991978394509507</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>9.70928912558888</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9.20707127950473</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>9.666922707527741</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>9.84553993325054</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>9.704899832704939</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.164406230334238</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>9,54; 9,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 9,93</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8,99; 9,14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,52; 9,71</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 9,91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,7</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 9,18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9,57; 9,7</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 9,88</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 9,62</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 9,13</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>9.637760359470542</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>9.80790121623571</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>9.509073108734622</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>9.057991276864716</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>9.621690256596413</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>9.792403738930492</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>9.601496861439047</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>9.106919397633346</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>9.629980759722818</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>9.800376348193176</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>9.554031594785314</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.081057911973323</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>9.539005799528955</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>9.715272555308113</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>9.42374014686669</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>8.988139821054755</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>9.524544694177933</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>9.691229195408974</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>9.513760991168251</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>9.044342265019466</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>9.566484641687268</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>9.722331055547787</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>9.484997006472435</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>9.029326328152754</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.73478873276642</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.934052406974539</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.603750309980549</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.143586783943322</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>9.711627205958811</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>9.907885398717834</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>9.698176989022093</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>9.181730494999783</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>9.698434500607341</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>9.884015437776576</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>9.622101629564806</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>9.131647260777667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
